--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -1,35 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_Plzeňský-KV" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SYSTEM" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="30_Plzeňský-KV" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SYSTEM" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +77,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,11 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8414,7 +8432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8458,6 +8476,23 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0031</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8531,6 +8566,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8568,6 +8608,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Mistr: HC Oceláři Třinec.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8605,6 +8650,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8642,6 +8692,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8679,6 +8734,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8716,6 +8776,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8753,6 +8818,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8790,6 +8860,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8827,6 +8902,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8864,6 +8944,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8901,6 +8986,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8938,6 +9028,11 @@
           <t>1.liga: základ + QF/SF + Play out + baráž.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8975,6 +9070,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9012,6 +9112,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9049,6 +9154,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9086,6 +9196,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9123,6 +9238,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9160,6 +9280,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9197,6 +9322,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9234,6 +9364,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9271,6 +9406,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9308,6 +9448,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9345,6 +9490,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9382,6 +9532,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9419,6 +9574,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9456,6 +9616,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9493,6 +9658,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9530,6 +9700,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9567,6 +9742,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9604,6 +9784,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9641,6 +9826,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9673,6 +9863,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9710,6 +9905,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9747,6 +9947,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9779,6 +9984,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9922,6 +10132,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0036</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9996,6 +10211,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0038</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10033,6 +10253,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10107,6 +10332,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0059</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10144,6 +10374,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0060</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10287,6 +10522,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0073</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10393,6 +10633,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0086</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10504,6 +10749,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0099</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10541,6 +10791,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0100</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10721,6 +10976,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0103</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10901,6 +11161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0128</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11007,6 +11272,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0137</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11113,6 +11383,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0148</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11256,6 +11531,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0161</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11362,6 +11642,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0186</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11505,6 +11790,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0199</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11646,6 +11936,11 @@
       <c r="J87" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0214</t>
         </is>
       </c>
     </row>
@@ -25889,6 +26184,81 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -8507,7 +8507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8569,6 +8569,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -8655,6 +8655,16 @@
           <t>NODE_S2020_21_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8664,6 +8674,14 @@
         <is>
           <t>NODE_S2019_20_0002</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -8739,6 +8757,16 @@
           <t>NODE_S2020_21_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8748,6 +8776,14 @@
         <is>
           <t>NODE_S2019_20_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -8781,6 +8817,12 @@
           <t>NODE_S2020_21_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8790,6 +8832,14 @@
         <is>
           <t>NODE_S2019_20_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -8823,6 +8873,16 @@
           <t>NODE_S2020_21_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8832,6 +8892,14 @@
         <is>
           <t>NODE_S2019_20_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -8865,6 +8933,8 @@
           <t>NODE_S2020_21_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8874,6 +8944,14 @@
         <is>
           <t>NODE_S2019_20_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -8907,6 +8985,8 @@
           <t>NODE_S2020_21_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8916,6 +8996,14 @@
         <is>
           <t>NODE_S2019_20_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -8949,6 +9037,8 @@
           <t>NODE_S2020_21_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8958,6 +9048,14 @@
         <is>
           <t>NODE_S2019_20_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -9075,6 +9173,16 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9084,6 +9192,14 @@
         <is>
           <t>NODE_S2019_20_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>18 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -9117,6 +9233,16 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9126,6 +9252,14 @@
         <is>
           <t>NODE_S2019_20_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -9159,6 +9293,12 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9168,6 +9308,14 @@
         <is>
           <t>NODE_S2019_20_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -9201,6 +9349,12 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9210,6 +9364,14 @@
         <is>
           <t>NODE_S2019_20_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -9243,6 +9405,8 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9252,6 +9416,14 @@
         <is>
           <t>NODE_S2019_20_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -9285,6 +9457,8 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9294,6 +9468,14 @@
         <is>
           <t>NODE_S2019_20_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -9579,6 +9761,12 @@
           <t>NODE_S2020_21_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9588,6 +9776,14 @@
         <is>
           <t>NODE_S2019_20_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -9621,6 +9817,12 @@
           <t>NODE_S2020_21_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9630,6 +9832,14 @@
         <is>
           <t>NODE_S2019_20_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -9663,6 +9873,12 @@
           <t>NODE_S2020_21_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9672,6 +9888,14 @@
         <is>
           <t>NODE_S2019_20_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -9705,6 +9929,8 @@
           <t>NODE_S2020_21_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9714,6 +9940,14 @@
         <is>
           <t>NODE_S2019_20_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -9747,6 +9981,8 @@
           <t>NODE_S2020_21_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9756,6 +9992,14 @@
         <is>
           <t>NODE_S2019_20_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">

--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -824,6 +824,11 @@
           <t>HC Oceláři Třinec</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>52</v>
       </c>
@@ -8822,7 +8827,6 @@
           <t>NODE_S2020_21_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8933,8 +8937,6 @@
           <t>NODE_S2020_21_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -8985,8 +8987,6 @@
           <t>NODE_S2020_21_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9037,8 +9037,6 @@
           <t>NODE_S2020_21_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9298,7 +9296,6 @@
           <t>NODE_S2020_21_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9354,7 +9351,6 @@
           <t>NODE_S2020_21_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9405,8 +9401,6 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9457,8 +9451,6 @@
           <t>NODE_S2020_21_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9766,7 +9758,6 @@
           <t>NODE_S2020_21_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9822,7 +9813,6 @@
           <t>NODE_S2020_21_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9878,7 +9868,6 @@
           <t>NODE_S2020_21_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9929,8 +9918,6 @@
           <t>NODE_S2020_21_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -9981,8 +9968,6 @@
           <t>NODE_S2020_21_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -26358,7 +26343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26430,6 +26415,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>1 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HC Oceláři Třinec</t>
         </is>
       </c>
     </row>

--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -2955,7 +2955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3688,6 +3688,118 @@
       <c r="U10" s="2" t="n"/>
       <c r="V10" s="2" t="n"/>
       <c r="W10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0092</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HC Stavební stroje Jičín</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0092</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0217</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00217</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0092</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0218</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00218</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4482,1767 +4594,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="3" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>row_type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>block_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>club_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>GP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>GF</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>comp_path</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>club_id</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dest_node_id</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dest_type</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>season_fate</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>tr_id</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HC Kohouti Česká Třebová</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0173</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00173</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HC Chotěboř (VYS)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M4" t="n">
-        <v>12</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0174</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00174</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HC Spartak Choceň</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" t="n">
-        <v>10</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0175</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00175</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HC Litomyšl</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>13</v>
-      </c>
-      <c r="M6" t="n">
-        <v>9</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0176</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00176</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HC Chrudim</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>13</v>
-      </c>
-      <c r="M7" t="n">
-        <v>9</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0177</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00177</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HC Slovan Moravská Třebová</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>17</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0178</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00178</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HC Světlá nad Sázavou (VYS)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>20</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0179</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00179</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HC Hlinsko</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>25</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0180</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00180</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HC Spartak Polička</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>33</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0181</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00181</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TJ Orli Lanškroun</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0076</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0182</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00182</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Krajská liga / Nedohráno pro Covid 19</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0077</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n"/>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n"/>
-      <c r="W13" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="3" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>row_type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>block_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>club_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>GP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>GF</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>comp_path</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>club_id</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prev_club_id</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dest_node_id</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dest_type</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>season_fate</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>tr_id</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SK Telč</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>14</v>
-      </c>
-      <c r="M3" t="n">
-        <v>7</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0183</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00183</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HC Skuteč (PCE)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0184</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00184</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HHK Velké Meziříčí "B"</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0185</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00185</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HC Zastávka (JM)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>12</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0186</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00186</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HC Ledeč nad Sázavou</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>13</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>16</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0187</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00187</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BK Zubři Bystřice nad Pernštejnem</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0188</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00188</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TJ Náměšť nad Oslavou</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>14</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0079</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0189</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00189</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Krajská liga / Nedohráno pro Covid 19</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0080</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Krajská liga / Nedohráno pro Covid 19 / HC Spartak Velká Bíteš B byl rozpuštěn</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0081</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6413,7 +4764,7 @@
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -6442,7 +4793,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SHKM Hodonín</t>
+          <t>HC Kohouti Česká Třebová</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -6458,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -6466,7 +4817,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -6478,7 +4829,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -6488,7 +4839,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0190</t>
+          <t>CLUB_S2020_21_0173</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6498,7 +4849,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00190</t>
+          <t>TR_S2020_21_00173</t>
         </is>
       </c>
     </row>
@@ -6515,28 +4866,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Moravskobudějovický Hokej (VYS)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>HC Chotěboř (VYS)</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6544,10 +4890,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -6556,7 +4902,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -6566,7 +4912,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0191</t>
+          <t>CLUB_S2020_21_0174</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6576,7 +4922,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00191</t>
+          <t>TR_S2020_21_00174</t>
         </is>
       </c>
     </row>
@@ -6593,7 +4939,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HC Lvi Břeclav</t>
+          <t>HC Spartak Choceň</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -6603,13 +4949,13 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -6617,10 +4963,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -6629,7 +4975,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -6639,7 +4985,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0192</t>
+          <t>CLUB_S2020_21_0175</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6649,7 +4995,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00192</t>
+          <t>TR_S2020_21_00175</t>
         </is>
       </c>
     </row>
@@ -6666,7 +5012,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HC Spartak Uherský Brod</t>
+          <t>HC Litomyšl</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -6682,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -6690,7 +5036,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
@@ -6702,7 +5048,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -6712,7 +5058,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0193</t>
+          <t>CLUB_S2020_21_0176</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6722,7 +5068,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00193</t>
+          <t>TR_S2020_21_00176</t>
         </is>
       </c>
     </row>
@@ -6739,14 +5085,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HK Kroměříž</t>
+          <t>HC Chrudim</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6755,7 +5101,7 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -6766,7 +5112,7 @@
         <v>13</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -6775,7 +5121,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -6785,7 +5131,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0194</t>
+          <t>CLUB_S2020_21_0177</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -6795,7 +5141,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00194</t>
+          <t>TR_S2020_21_00177</t>
         </is>
       </c>
     </row>
@@ -6812,23 +5158,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SKMB Boskovice</t>
+          <t>HC Slovan Moravská Třebová</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -6836,10 +5182,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -6848,7 +5194,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -6858,7 +5204,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0195</t>
+          <t>CLUB_S2020_21_0178</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -6868,7 +5214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00195</t>
+          <t>TR_S2020_21_00178</t>
         </is>
       </c>
     </row>
@@ -6885,23 +5231,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dynamiters Blansko HK</t>
+          <t>HC Světlá nad Sázavou (VYS)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -6909,10 +5255,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -6921,7 +5267,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -6931,7 +5277,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0196</t>
+          <t>CLUB_S2020_21_0179</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -6941,7 +5287,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00196</t>
+          <t>TR_S2020_21_00179</t>
         </is>
       </c>
     </row>
@@ -6958,11 +5304,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HC Štika Rosice</t>
+          <t>HC Hlinsko</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -6971,10 +5317,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -6982,10 +5328,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -6994,7 +5340,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -7004,7 +5350,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0197</t>
+          <t>CLUB_S2020_21_0180</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -7014,7 +5360,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00197</t>
+          <t>TR_S2020_21_00180</t>
         </is>
       </c>
     </row>
@@ -7031,7 +5377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HC Brumov-Bylnice</t>
+          <t>HC Spartak Polička</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -7041,13 +5392,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -7055,10 +5406,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -7067,7 +5418,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -7077,7 +5428,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0198</t>
+          <t>CLUB_S2020_21_0181</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -7087,7 +5438,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00198</t>
+          <t>TR_S2020_21_00181</t>
         </is>
       </c>
     </row>
@@ -7104,11 +5455,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hokej Uherský Ostroh</t>
+          <t>TJ Orli Lanškroun</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7117,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -7128,10 +5479,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -7140,7 +5491,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>NODE_S2020_21_0083</t>
+          <t>NODE_S2020_21_0076</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -7150,7 +5501,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CLUB_S2020_21_0199</t>
+          <t>CLUB_S2020_21_0182</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -7160,236 +5511,165 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>TR_S2020_21_00199</t>
+          <t>TR_S2020_21_00182</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HC Uherské Hradiště</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>9</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>16</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Krajská liga</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0083</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0200</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00200</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Krajská liga / Nedohráno pro Covid 19</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0077</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="n"/>
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="n"/>
+      <c r="W13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0093</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>T</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HC Spartak Velká Bíteš (VYS)</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>8</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>15</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Krajská liga</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0083</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>L30</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>CLUB_S2020_21_0201</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>setrval</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>TR_S2020_21_00201</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Krajská liga / Nedohráno pro Covid 19</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0084</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
-      <c r="T15" s="2" t="n"/>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="n"/>
-      <c r="W15" s="2" t="n"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0093</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0219</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00219</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Krajská liga / Nedohráno pro Covid 19 / TJ Sokol Březina hokej zde skončil</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>NODE_S2020_21_0085</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
-      <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="n"/>
-      <c r="W16" s="2" t="n"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0093</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0220</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00220</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7565,6 +5845,2174 @@
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SK Telč</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0183</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00183</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HC Skuteč (PCE)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0184</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00184</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HHK Velké Meziříčí "B"</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0185</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00185</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HC Zastávka (JM)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0186</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00186</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>16</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0187</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00187</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BK Zubři Bystřice nad Pernštejnem</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0188</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00188</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TJ Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0079</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0189</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00189</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Krajská liga / Nedohráno pro Covid 19</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0080</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Krajská liga / Nedohráno pro Covid 19 / HC Spartak Velká Bíteš B byl rozpuštěn</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0081</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n"/>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0094</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0094</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0221</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00221</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0094</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0222</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00222</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHKM Hodonín</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>12</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0190</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00190</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Moravskobudějovický Hokej (VYS)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0191</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00191</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HC Lvi Břeclav</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0192</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00192</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HC Spartak Uherský Brod</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0193</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00193</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HK Kroměříž</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>13</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0194</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00194</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SKMB Boskovice</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>14</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0195</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00195</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dynamiters Blansko HK</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>21</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0196</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00196</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HC Štika Rosice</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>14</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0197</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00197</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HC Brumov-Bylnice</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0198</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00198</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hokej Uherský Ostroh</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0199</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00199</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HC Uherské Hradiště</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>16</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0200</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HC Spartak Velká Bíteš (VYS)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0083</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0201</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00201</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Krajská liga / Nedohráno pro Covid 19</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0084</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n"/>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n"/>
+      <c r="W15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Krajská liga / Nedohráno pro Covid 19 / TJ Sokol Březina hokej zde skončil</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0085</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0095</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Moravskobudějovický Hokej</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0095</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0223</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00223</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HC Spartak Velká Bíteš</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0095</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0224</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00224</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>NODE_S2020_21_0087</t>
         </is>
       </c>
@@ -8425,6 +8873,118 @@
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0096</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HC Uničov</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0096</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0225</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00225</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HC Rožnov pod Radhoštěm</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0096</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0226</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00226</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8512,7 +9072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12254,6 +12814,302 @@
       <c r="J89" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Praha – Přebor Prahy</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>REG_PHA</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0034</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Středočeský – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0038</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Plzeňský – Krajská soutěž</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>REG_PLK</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0051</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>REG_LBK</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0068</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0075</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0078</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0082</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Severomoravský – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0086</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -16280,7 +17136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:J227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -26329,6 +27185,384 @@
       <c r="J213" t="inlineStr">
         <is>
           <t>Krnov</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>HC Berounští Medvědi</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>HC Berounští Medvědi</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HC Letci Letňany "B"</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>HC Letci Letňany "B"</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SK Žižkov Praha</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SK Žižkov Praha</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HC Spartak Žebrák "B"</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HC Spartak Žebrák "B"</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HC Stavební stroje Jičín</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>HC Stavební stroje Jičín</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Moravskobudějovický Hokej</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Moravskobudějovický Hokej</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HC Spartak Velká Bíteš</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>HC Spartak Velká Bíteš</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HC Uničov</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>HC Uničov</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>HC Rožnov pod Radhoštěm</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>HC Rožnov pod Radhoštěm</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>
@@ -28933,7 +30167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -29631,6 +30865,73 @@
       <c r="V10" s="2" t="n"/>
       <c r="W10" s="2" t="n"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Přebor Prahy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0089</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HC Berounští Medvědi</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Přebor Prahy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0089</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0213</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00213</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29642,7 +30943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32431,6 +33732,118 @@
       <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="n"/>
       <c r="W41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0090</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HC Letci Letňany "B"</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0090</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0214</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00214</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SK Žižkov Praha</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0090</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0215</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00215</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33631,7 +35044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -36292,6 +37705,73 @@
       <c r="U39" s="2" t="n"/>
       <c r="V39" s="2" t="n"/>
       <c r="W39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Krajská soutěž</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0091</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HC Spartak Žebrák "B"</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Krajská soutěž</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0091</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2020_21_0216</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2020_21_00216</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +86,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +115,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -27675,7 +27686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27732,11 +27743,219 @@
           <t>NODE_S2020_21_0031</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Přebor Prahy (Praha) · NODE_S2020_21_0089</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Berounští Medvědi), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Středočeský – Krajská liga (Středočeský kraj) · NODE_S2020_21_0090</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Letci Letňany "B", SK Žižkov Praha), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Plzeňský – Krajská soutěž (Plzeňský kraj) · NODE_S2020_21_0091</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Spartak Žebrák "B"), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2020_21_0092</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Stavební stroje Jičín, HC TS Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga (Pardubický kraj) · NODE_S2020_21_0093</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Chotěboř, HC Světlá nad Sázavou), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga (Vysočina) · NODE_S2020_21_0094</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Skuteč, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Krajská liga (Jihomoravský kraj) · NODE_S2020_21_0095</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (Moravskobudějovický Hokej, HC Spartak Velká Bíteš), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Severomoravský – Krajská liga (jihozápadní Morava) · NODE_S2020_21_0096</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Uničov, HC Rožnov pod Radhoštěm), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9008,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9067,6 +9070,142 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0089</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Berounští Medvědi), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0090</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Letci Letňany "B", SK Žižkov Praha), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0091</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Spartak Žebrák "B"), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0092</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Stavební stroje Jičín, HC TS Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0093</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Chotěboř, HC Světlá nad Sázavou), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0094</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Skuteč, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0095</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (Moravskobudějovický Hokej, HC Spartak Velká Bíteš), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NODE_S2020_21_0096</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Uničov, HC Rožnov pod Radhoštěm), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -27763,7 +27902,7 @@
           <t>Praha – Přebor Prahy (Praha) · NODE_S2020_21_0089</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Berounští Medvědi), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -27789,7 +27928,7 @@
           <t>Středočeský – Krajská liga (Středočeský kraj) · NODE_S2020_21_0090</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Letci Letňany "B", SK Žižkov Praha), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -27815,7 +27954,7 @@
           <t>Plzeňský – Krajská soutěž (Plzeňský kraj) · NODE_S2020_21_0091</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Spartak Žebrák "B"), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -27841,7 +27980,7 @@
           <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2020_21_0092</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Stavební stroje Jičín, HC TS Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -27867,7 +28006,7 @@
           <t>Pardubický – Krajská liga (Pardubický kraj) · NODE_S2020_21_0093</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Chotěboř, HC Světlá nad Sázavou), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -27893,7 +28032,7 @@
           <t>Vysočina – Krajská liga (Vysočina) · NODE_S2020_21_0094</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Skuteč, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -27919,7 +28058,7 @@
           <t>Jihomoravský – Krajská liga (Jihomoravský kraj) · NODE_S2020_21_0095</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (Moravskobudějovický Hokej, HC Spartak Velká Bíteš), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -27945,7 +28084,7 @@
           <t>Severomoravský – Krajská liga (jihozápadní Morava) · NODE_S2020_21_0096</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Uničov, HC Rožnov pod Radhoštěm), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2020_21_FINAL.xlsx
+++ b/data/S2020_21_FINAL.xlsx
@@ -10910,7 +10910,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HC Pubec Plzeň  hokej zde zanikl</t>
+          <t>HC Pubec Plzeň hokej zde zanikl</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SKP Rapid Plzeň  hokej zde zanikl</t>
+          <t>SKP Rapid Plzeň hokej zde zanikl</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Plzeňský-KV L40</t>
+          <t>Plzeňský-KV, 4. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
